--- a/human_resources_forms/038_employee_wellness_leave_form--human_resources_forms.xlsx
+++ b/human_resources_forms/038_employee_wellness_leave_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'assistant_manager'}</t>
+          <t>assistant_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Assistant Manager'}</t>
+          <t>Assistant Manager</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
